--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-patient.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T15:13:06+00:00</t>
+    <t>2026-02-18T10:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1218,7 +1218,7 @@
     <t>Patient.extension:TDDUIHouseholdSituation.extension:householdComposition.value[x]:valueCodeableConcept</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J385-composition-foyer-ms/FHIR/JDV-J385-composition-foyer-ms</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j385-composition-foyer-ms</t>
   </si>
   <si>
     <t>Patient.extension:TDDUIHouseholdSituation.extension:householdCompositionDescription</t>

--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-patient.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9221" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9221" uniqueCount="1056">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T10:14:45+00:00</t>
+    <t>2026-02-24T10:54:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -692,7 +692,7 @@
     <t>Carries the death place of the patient |Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).</t>
   </si>
   <si>
-    <t>paysDeces</t>
+    <t>communeDeces/departementDeces/paysDeces</t>
   </si>
   <si>
     <t>Patient.extension:birthdateUpdateIndicator</t>
@@ -1634,7 +1634,7 @@
     <t>Hospital assigned patient identifier | IPP; Dans le cadre de ce volet, représente l'Identifiant local de l’usager au sein de la structure.</t>
   </si>
   <si>
-    <t>identifiantLocalUsagerESSMS</t>
+    <t>identifiantUsagerESSMS</t>
   </si>
   <si>
     <t>Patient.identifier:PI.id</t>
@@ -2549,9 +2549,6 @@
   </si>
   <si>
     <t>Patient.address.id</t>
-  </si>
-  <si>
-    <t>idAdresse</t>
   </si>
   <si>
     <t>Patient.address.extension</t>
@@ -3685,7 +3682,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="30.4765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="38.2578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="134.453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="34.98828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -25509,7 +25506,7 @@
         <v>82</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>807</v>
+        <v>82</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>109</v>
@@ -25529,10 +25526,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25649,10 +25646,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>252</v>
@@ -25680,7 +25677,7 @@
         <v>253</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M184" t="s" s="2">
         <v>255</v>
@@ -25769,10 +25766,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C185" t="s" s="2">
         <v>398</v>
@@ -25889,10 +25886,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26011,10 +26008,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26111,7 +26108,7 @@
         <v>103</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>267</v>
@@ -26131,10 +26128,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26253,10 +26250,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26371,10 +26368,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26489,10 +26486,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26605,13 +26602,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C192" t="s" s="2">
         <v>819</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C192" t="s" s="2">
-        <v>820</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>82</v>
@@ -26633,13 +26630,13 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="L192" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="L192" t="s" s="2">
+      <c r="M192" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -26708,7 +26705,7 @@
         <v>82</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>82</v>
@@ -26725,13 +26722,13 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C193" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C193" t="s" s="2">
-        <v>826</v>
       </c>
       <c r="D193" t="s" s="2">
         <v>82</v>
@@ -26753,13 +26750,13 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>827</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -26825,10 +26822,10 @@
         <v>120</v>
       </c>
       <c r="AK193" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="AL193" t="s" s="2">
         <v>829</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>830</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>82</v>
@@ -26845,13 +26842,13 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C194" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="D194" t="s" s="2">
         <v>82</v>
@@ -26873,13 +26870,13 @@
         <v>82</v>
       </c>
       <c r="K194" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>833</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>834</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -26945,10 +26942,10 @@
         <v>120</v>
       </c>
       <c r="AK194" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="AL194" t="s" s="2">
         <v>835</v>
-      </c>
-      <c r="AL194" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>82</v>
@@ -26965,13 +26962,13 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C195" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C195" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="D195" t="s" s="2">
         <v>82</v>
@@ -26993,13 +26990,13 @@
         <v>82</v>
       </c>
       <c r="K195" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="L195" t="s" s="2">
         <v>839</v>
       </c>
-      <c r="L195" t="s" s="2">
+      <c r="M195" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>841</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -27068,7 +27065,7 @@
         <v>82</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>82</v>
@@ -27085,13 +27082,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C196" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C196" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>82</v>
@@ -27113,13 +27110,13 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="L196" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="L196" t="s" s="2">
+      <c r="M196" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>847</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -27188,7 +27185,7 @@
         <v>82</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>82</v>
@@ -27205,10 +27202,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="B197" t="s" s="2">
         <v>849</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>850</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27323,10 +27320,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="B198" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27441,10 +27438,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="B199" t="s" s="2">
         <v>853</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>854</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -27484,7 +27481,7 @@
       </c>
       <c r="Q199" s="2"/>
       <c r="R199" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="S199" t="s" s="2">
         <v>82</v>
@@ -27561,10 +27558,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="B200" t="s" s="2">
         <v>856</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>857</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27593,7 +27590,7 @@
         <v>371</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -27624,7 +27621,7 @@
       </c>
       <c r="Y200" s="2"/>
       <c r="Z200" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>82</v>
@@ -27651,7 +27648,7 @@
         <v>91</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>103</v>
@@ -27677,13 +27674,13 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C201" t="s" s="2">
         <v>861</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C201" t="s" s="2">
-        <v>862</v>
       </c>
       <c r="D201" t="s" s="2">
         <v>82</v>
@@ -27705,13 +27702,13 @@
         <v>82</v>
       </c>
       <c r="K201" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="L201" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="M201" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="L201" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="M201" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -27777,10 +27774,10 @@
         <v>120</v>
       </c>
       <c r="AK201" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="AL201" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="AL201" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>82</v>
@@ -27797,13 +27794,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>867</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>868</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>82</v>
@@ -27825,13 +27822,13 @@
         <v>82</v>
       </c>
       <c r="K202" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="L202" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="M202" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="L202" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -27897,10 +27894,10 @@
         <v>120</v>
       </c>
       <c r="AK202" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="AL202" t="s" s="2">
         <v>871</v>
-      </c>
-      <c r="AL202" t="s" s="2">
-        <v>872</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>82</v>
@@ -27917,13 +27914,13 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C203" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="D203" t="s" s="2">
         <v>82</v>
@@ -27945,13 +27942,13 @@
         <v>82</v>
       </c>
       <c r="K203" t="s" s="2">
+        <v>874</v>
+      </c>
+      <c r="L203" t="s" s="2">
         <v>875</v>
       </c>
-      <c r="L203" t="s" s="2">
+      <c r="M203" t="s" s="2">
         <v>876</v>
-      </c>
-      <c r="M203" t="s" s="2">
-        <v>877</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -28037,10 +28034,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -28066,7 +28063,7 @@
         <v>105</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="M204" t="s" s="2">
         <v>789</v>
@@ -28093,34 +28090,34 @@
         <v>82</v>
       </c>
       <c r="W204" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="X204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF204" t="s" s="2">
         <v>880</v>
-      </c>
-      <c r="X204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF204" t="s" s="2">
-        <v>881</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -28155,10 +28152,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -28273,10 +28270,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28391,10 +28388,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28489,7 +28486,7 @@
         <v>103</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>323</v>
@@ -28509,10 +28506,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28607,7 +28604,7 @@
         <v>103</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="AL208" t="s" s="2">
         <v>332</v>
@@ -28627,10 +28624,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28692,7 +28689,7 @@
       </c>
       <c r="Y209" s="2"/>
       <c r="Z209" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>82</v>
@@ -28725,7 +28722,7 @@
         <v>103</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="AL209" t="s" s="2">
         <v>340</v>
@@ -28745,10 +28742,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28865,10 +28862,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28894,14 +28891,14 @@
         <v>376</v>
       </c>
       <c r="L211" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="M211" t="s" s="2">
         <v>893</v>
-      </c>
-      <c r="M211" t="s" s="2">
-        <v>894</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>82</v>
@@ -28930,7 +28927,7 @@
       </c>
       <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>82</v>
@@ -28948,7 +28945,7 @@
         <v>82</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -28966,16 +28963,16 @@
         <v>82</v>
       </c>
       <c r="AL211" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="AM211" t="s" s="2">
         <v>897</v>
       </c>
-      <c r="AM211" t="s" s="2">
+      <c r="AN211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO211" t="s" s="2">
         <v>898</v>
-      </c>
-      <c r="AN211" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO211" t="s" s="2">
-        <v>899</v>
       </c>
       <c r="AP211" t="s" s="2">
         <v>82</v>
@@ -28983,10 +28980,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -29009,19 +29006,19 @@
         <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="L212" t="s" s="2">
         <v>901</v>
       </c>
-      <c r="L212" t="s" s="2">
+      <c r="M212" t="s" s="2">
         <v>902</v>
       </c>
-      <c r="M212" t="s" s="2">
+      <c r="N212" t="s" s="2">
         <v>903</v>
       </c>
-      <c r="N212" t="s" s="2">
+      <c r="O212" t="s" s="2">
         <v>904</v>
-      </c>
-      <c r="O212" t="s" s="2">
-        <v>905</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>82</v>
@@ -29070,7 +29067,7 @@
         <v>82</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -29088,7 +29085,7 @@
         <v>82</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>109</v>
@@ -29097,7 +29094,7 @@
         <v>82</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AP212" t="s" s="2">
         <v>82</v>
@@ -29105,10 +29102,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29131,19 +29128,19 @@
         <v>82</v>
       </c>
       <c r="K213" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="L213" t="s" s="2">
         <v>909</v>
       </c>
-      <c r="L213" t="s" s="2">
+      <c r="M213" t="s" s="2">
         <v>910</v>
       </c>
-      <c r="M213" t="s" s="2">
+      <c r="N213" t="s" s="2">
         <v>911</v>
       </c>
-      <c r="N213" t="s" s="2">
+      <c r="O213" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>82</v>
@@ -29192,7 +29189,7 @@
         <v>82</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -29207,10 +29204,10 @@
         <v>103</v>
       </c>
       <c r="AK213" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="AL213" t="s" s="2">
         <v>914</v>
-      </c>
-      <c r="AL213" t="s" s="2">
-        <v>915</v>
       </c>
       <c r="AM213" t="s" s="2">
         <v>109</v>
@@ -29219,7 +29216,7 @@
         <v>82</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="AP213" t="s" s="2">
         <v>82</v>
@@ -29227,10 +29224,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29253,19 +29250,19 @@
         <v>82</v>
       </c>
       <c r="K214" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="L214" t="s" s="2">
         <v>918</v>
       </c>
-      <c r="L214" t="s" s="2">
+      <c r="M214" t="s" s="2">
         <v>919</v>
       </c>
-      <c r="M214" t="s" s="2">
+      <c r="N214" t="s" s="2">
         <v>920</v>
       </c>
-      <c r="N214" t="s" s="2">
+      <c r="O214" t="s" s="2">
         <v>921</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>922</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>82</v>
@@ -29314,7 +29311,7 @@
         <v>82</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -29326,13 +29323,13 @@
         <v>82</v>
       </c>
       <c r="AJ214" t="s" s="2">
+        <v>922</v>
+      </c>
+      <c r="AK214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL214" t="s" s="2">
         <v>923</v>
-      </c>
-      <c r="AK214" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL214" t="s" s="2">
-        <v>924</v>
       </c>
       <c r="AM214" t="s" s="2">
         <v>109</v>
@@ -29349,10 +29346,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -29467,10 +29464,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29583,13 +29580,13 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="C217" t="s" s="2">
         <v>927</v>
-      </c>
-      <c r="B217" t="s" s="2">
-        <v>926</v>
-      </c>
-      <c r="C217" t="s" s="2">
-        <v>928</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>82</v>
@@ -29611,13 +29608,13 @@
         <v>82</v>
       </c>
       <c r="K217" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="L217" t="s" s="2">
         <v>929</v>
       </c>
-      <c r="L217" t="s" s="2">
+      <c r="M217" t="s" s="2">
         <v>930</v>
-      </c>
-      <c r="M217" t="s" s="2">
-        <v>931</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -29703,13 +29700,13 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="C218" t="s" s="2">
         <v>932</v>
-      </c>
-      <c r="B218" t="s" s="2">
-        <v>926</v>
-      </c>
-      <c r="C218" t="s" s="2">
-        <v>933</v>
       </c>
       <c r="D218" t="s" s="2">
         <v>82</v>
@@ -29731,13 +29728,13 @@
         <v>82</v>
       </c>
       <c r="K218" t="s" s="2">
+        <v>933</v>
+      </c>
+      <c r="L218" t="s" s="2">
         <v>934</v>
       </c>
-      <c r="L218" t="s" s="2">
+      <c r="M218" t="s" s="2">
         <v>935</v>
-      </c>
-      <c r="M218" t="s" s="2">
-        <v>936</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -29823,14 +29820,14 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
@@ -29852,10 +29849,10 @@
         <v>112</v>
       </c>
       <c r="L219" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="M219" t="s" s="2">
         <v>939</v>
-      </c>
-      <c r="M219" t="s" s="2">
-        <v>940</v>
       </c>
       <c r="N219" t="s" s="2">
         <v>115</v>
@@ -29910,7 +29907,7 @@
         <v>82</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
@@ -29945,10 +29942,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29974,14 +29971,14 @@
         <v>376</v>
       </c>
       <c r="L220" t="s" s="2">
+        <v>942</v>
+      </c>
+      <c r="M220" t="s" s="2">
         <v>943</v>
-      </c>
-      <c r="M220" t="s" s="2">
-        <v>944</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>82</v>
@@ -30009,16 +30006,16 @@
         <v>153</v>
       </c>
       <c r="Y220" t="s" s="2">
+        <v>945</v>
+      </c>
+      <c r="Z220" t="s" s="2">
         <v>946</v>
       </c>
-      <c r="Z220" t="s" s="2">
+      <c r="AA220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB220" t="s" s="2">
         <v>947</v>
-      </c>
-      <c r="AA220" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB220" t="s" s="2">
-        <v>948</v>
       </c>
       <c r="AC220" s="2"/>
       <c r="AD220" t="s" s="2">
@@ -30028,7 +30025,7 @@
         <v>118</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
@@ -30046,7 +30043,7 @@
         <v>82</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>109</v>
@@ -30055,7 +30052,7 @@
         <v>82</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AP220" t="s" s="2">
         <v>82</v>
@@ -30063,13 +30060,13 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>941</v>
+      </c>
+      <c r="C221" t="s" s="2">
         <v>951</v>
-      </c>
-      <c r="B221" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="C221" t="s" s="2">
-        <v>952</v>
       </c>
       <c r="D221" t="s" s="2">
         <v>82</v>
@@ -30094,14 +30091,14 @@
         <v>376</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>82</v>
@@ -30130,7 +30127,7 @@
       </c>
       <c r="Y221" s="2"/>
       <c r="Z221" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="AA221" t="s" s="2">
         <v>82</v>
@@ -30148,7 +30145,7 @@
         <v>82</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
@@ -30166,7 +30163,7 @@
         <v>82</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>109</v>
@@ -30175,7 +30172,7 @@
         <v>82</v>
       </c>
       <c r="AO221" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AP221" t="s" s="2">
         <v>82</v>
@@ -30183,13 +30180,13 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
+        <v>954</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>941</v>
+      </c>
+      <c r="C222" t="s" s="2">
         <v>955</v>
-      </c>
-      <c r="B222" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="C222" t="s" s="2">
-        <v>956</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>82</v>
@@ -30214,14 +30211,14 @@
         <v>376</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>82</v>
@@ -30250,7 +30247,7 @@
       </c>
       <c r="Y222" s="2"/>
       <c r="Z222" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="AA222" t="s" s="2">
         <v>82</v>
@@ -30268,7 +30265,7 @@
         <v>82</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
@@ -30286,7 +30283,7 @@
         <v>82</v>
       </c>
       <c r="AL222" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AM222" t="s" s="2">
         <v>109</v>
@@ -30295,7 +30292,7 @@
         <v>82</v>
       </c>
       <c r="AO222" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AP222" t="s" s="2">
         <v>82</v>
@@ -30303,10 +30300,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -30329,19 +30326,19 @@
         <v>82</v>
       </c>
       <c r="K223" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="L223" t="s" s="2">
         <v>960</v>
       </c>
-      <c r="L223" t="s" s="2">
+      <c r="M223" t="s" s="2">
         <v>961</v>
       </c>
-      <c r="M223" t="s" s="2">
+      <c r="N223" t="s" s="2">
         <v>962</v>
       </c>
-      <c r="N223" t="s" s="2">
+      <c r="O223" t="s" s="2">
         <v>963</v>
-      </c>
-      <c r="O223" t="s" s="2">
-        <v>964</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>82</v>
@@ -30390,7 +30387,7 @@
         <v>82</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -30408,16 +30405,16 @@
         <v>82</v>
       </c>
       <c r="AL223" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="AM223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO223" t="s" s="2">
         <v>965</v>
-      </c>
-      <c r="AM223" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN223" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO223" t="s" s="2">
-        <v>966</v>
       </c>
       <c r="AP223" t="s" s="2">
         <v>82</v>
@@ -30425,10 +30422,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -30460,7 +30457,7 @@
         <v>704</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="O224" t="s" s="2">
         <v>706</v>
@@ -30512,7 +30509,7 @@
         <v>82</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -30547,10 +30544,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30573,17 +30570,17 @@
         <v>82</v>
       </c>
       <c r="K225" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="L225" t="s" s="2">
         <v>970</v>
       </c>
-      <c r="L225" t="s" s="2">
+      <c r="M225" t="s" s="2">
         <v>971</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>972</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>82</v>
@@ -30632,7 +30629,7 @@
         <v>82</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -30650,7 +30647,7 @@
         <v>82</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="AM225" t="s" s="2">
         <v>109</v>
@@ -30659,7 +30656,7 @@
         <v>82</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>82</v>
@@ -30667,10 +30664,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30696,14 +30693,14 @@
         <v>171</v>
       </c>
       <c r="L226" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="M226" t="s" s="2">
         <v>977</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>978</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>82</v>
@@ -30731,11 +30728,11 @@
         <v>263</v>
       </c>
       <c r="Y226" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="Z226" t="s" s="2">
         <v>980</v>
       </c>
-      <c r="Z226" t="s" s="2">
-        <v>981</v>
-      </c>
       <c r="AA226" t="s" s="2">
         <v>82</v>
       </c>
@@ -30752,7 +30749,7 @@
         <v>82</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
@@ -30779,7 +30776,7 @@
         <v>82</v>
       </c>
       <c r="AO226" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="AP226" t="s" s="2">
         <v>82</v>
@@ -30787,10 +30784,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30816,14 +30813,14 @@
         <v>462</v>
       </c>
       <c r="L227" t="s" s="2">
+        <v>983</v>
+      </c>
+      <c r="M227" t="s" s="2">
         <v>984</v>
-      </c>
-      <c r="M227" t="s" s="2">
-        <v>985</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>82</v>
@@ -30872,7 +30869,7 @@
         <v>82</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -30881,7 +30878,7 @@
         <v>91</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AJ227" t="s" s="2">
         <v>103</v>
@@ -30890,7 +30887,7 @@
         <v>82</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>109</v>
@@ -30899,7 +30896,7 @@
         <v>82</v>
       </c>
       <c r="AO227" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AP227" t="s" s="2">
         <v>82</v>
@@ -30907,10 +30904,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30936,10 +30933,10 @@
         <v>344</v>
       </c>
       <c r="L228" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="M228" t="s" s="2">
         <v>991</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>992</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -30990,7 +30987,7 @@
         <v>82</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
@@ -31008,7 +31005,7 @@
         <v>82</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>109</v>
@@ -31025,10 +31022,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -31051,19 +31048,19 @@
         <v>82</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="L229" t="s" s="2">
+        <v>994</v>
+      </c>
+      <c r="M229" t="s" s="2">
         <v>995</v>
       </c>
-      <c r="M229" t="s" s="2">
+      <c r="N229" t="s" s="2">
         <v>996</v>
       </c>
-      <c r="N229" t="s" s="2">
+      <c r="O229" t="s" s="2">
         <v>997</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>998</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>82</v>
@@ -31112,7 +31109,7 @@
         <v>82</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
@@ -31130,10 +31127,10 @@
         <v>82</v>
       </c>
       <c r="AL229" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="AM229" t="s" s="2">
         <v>999</v>
-      </c>
-      <c r="AM229" t="s" s="2">
-        <v>1000</v>
       </c>
       <c r="AN229" t="s" s="2">
         <v>82</v>
@@ -31147,10 +31144,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31265,10 +31262,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31385,14 +31382,14 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
@@ -31414,10 +31411,10 @@
         <v>112</v>
       </c>
       <c r="L232" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="M232" t="s" s="2">
         <v>939</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>940</v>
       </c>
       <c r="N232" t="s" s="2">
         <v>115</v>
@@ -31472,7 +31469,7 @@
         <v>82</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
@@ -31507,10 +31504,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -31536,16 +31533,16 @@
         <v>376</v>
       </c>
       <c r="L233" t="s" s="2">
+        <v>1004</v>
+      </c>
+      <c r="M233" t="s" s="2">
         <v>1005</v>
       </c>
-      <c r="M233" t="s" s="2">
+      <c r="N233" t="s" s="2">
         <v>1006</v>
       </c>
-      <c r="N233" t="s" s="2">
+      <c r="O233" t="s" s="2">
         <v>1007</v>
-      </c>
-      <c r="O233" t="s" s="2">
-        <v>1008</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>82</v>
@@ -31574,7 +31571,7 @@
       </c>
       <c r="Y233" s="2"/>
       <c r="Z233" t="s" s="2">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>82</v>
@@ -31592,7 +31589,7 @@
         <v>82</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>91</v>
@@ -31607,19 +31604,19 @@
         <v>103</v>
       </c>
       <c r="AK233" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="AL233" t="s" s="2">
         <v>1010</v>
       </c>
-      <c r="AL233" t="s" s="2">
+      <c r="AM233" t="s" s="2">
         <v>1011</v>
       </c>
-      <c r="AM233" t="s" s="2">
+      <c r="AN233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO233" t="s" s="2">
         <v>1012</v>
-      </c>
-      <c r="AN233" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO233" t="s" s="2">
-        <v>1013</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>82</v>
@@ -31627,10 +31624,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -31656,16 +31653,16 @@
         <v>595</v>
       </c>
       <c r="L234" t="s" s="2">
+        <v>1014</v>
+      </c>
+      <c r="M234" t="s" s="2">
         <v>1015</v>
       </c>
-      <c r="M234" t="s" s="2">
+      <c r="N234" t="s" s="2">
         <v>1016</v>
       </c>
-      <c r="N234" t="s" s="2">
+      <c r="O234" t="s" s="2">
         <v>1017</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>1018</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>82</v>
@@ -31714,7 +31711,7 @@
         <v>82</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
@@ -31732,16 +31729,16 @@
         <v>82</v>
       </c>
       <c r="AL234" t="s" s="2">
+        <v>1018</v>
+      </c>
+      <c r="AM234" t="s" s="2">
         <v>1019</v>
       </c>
-      <c r="AM234" t="s" s="2">
+      <c r="AN234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO234" t="s" s="2">
         <v>1020</v>
-      </c>
-      <c r="AN234" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO234" t="s" s="2">
-        <v>1021</v>
       </c>
       <c r="AP234" t="s" s="2">
         <v>82</v>
@@ -31749,14 +31746,14 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
@@ -31775,16 +31772,16 @@
         <v>82</v>
       </c>
       <c r="K235" t="s" s="2">
+        <v>1023</v>
+      </c>
+      <c r="L235" t="s" s="2">
         <v>1024</v>
       </c>
-      <c r="L235" t="s" s="2">
+      <c r="M235" t="s" s="2">
         <v>1025</v>
       </c>
-      <c r="M235" t="s" s="2">
+      <c r="N235" t="s" s="2">
         <v>1026</v>
-      </c>
-      <c r="N235" t="s" s="2">
-        <v>1027</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
@@ -31834,7 +31831,7 @@
         <v>82</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>80</v>
@@ -31852,7 +31849,7 @@
         <v>82</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AM235" t="s" s="2">
         <v>109</v>
@@ -31861,7 +31858,7 @@
         <v>82</v>
       </c>
       <c r="AO235" t="s" s="2">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AP235" t="s" s="2">
         <v>82</v>
@@ -31869,10 +31866,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -31895,19 +31892,19 @@
         <v>92</v>
       </c>
       <c r="K236" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="L236" t="s" s="2">
         <v>1031</v>
       </c>
-      <c r="L236" t="s" s="2">
+      <c r="M236" t="s" s="2">
         <v>1032</v>
       </c>
-      <c r="M236" t="s" s="2">
+      <c r="N236" t="s" s="2">
         <v>1033</v>
       </c>
-      <c r="N236" t="s" s="2">
+      <c r="O236" t="s" s="2">
         <v>1034</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>1035</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>82</v>
@@ -31956,7 +31953,7 @@
         <v>82</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
@@ -31974,10 +31971,10 @@
         <v>82</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AM236" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AN236" t="s" s="2">
         <v>82</v>
@@ -31991,10 +31988,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -32017,19 +32014,19 @@
         <v>92</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="L237" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="M237" t="s" s="2">
         <v>1038</v>
       </c>
-      <c r="M237" t="s" s="2">
+      <c r="N237" t="s" s="2">
         <v>1039</v>
       </c>
-      <c r="N237" t="s" s="2">
+      <c r="O237" t="s" s="2">
         <v>1040</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>1041</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>82</v>
@@ -32078,7 +32075,7 @@
         <v>82</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>80</v>
@@ -32096,7 +32093,7 @@
         <v>82</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="AM237" t="s" s="2">
         <v>109</v>
@@ -32113,10 +32110,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -32231,10 +32228,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -32351,14 +32348,14 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
@@ -32380,10 +32377,10 @@
         <v>112</v>
       </c>
       <c r="L240" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="M240" t="s" s="2">
         <v>939</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>940</v>
       </c>
       <c r="N240" t="s" s="2">
         <v>115</v>
@@ -32438,7 +32435,7 @@
         <v>82</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>80</v>
@@ -32473,10 +32470,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -32499,16 +32496,16 @@
         <v>92</v>
       </c>
       <c r="K241" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="L241" t="s" s="2">
         <v>1047</v>
       </c>
-      <c r="L241" t="s" s="2">
+      <c r="M241" t="s" s="2">
         <v>1048</v>
       </c>
-      <c r="M241" t="s" s="2">
+      <c r="N241" t="s" s="2">
         <v>1049</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>1050</v>
       </c>
       <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
@@ -32558,7 +32555,7 @@
         <v>82</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>91</v>
@@ -32585,7 +32582,7 @@
         <v>82</v>
       </c>
       <c r="AO241" t="s" s="2">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="AP241" t="s" s="2">
         <v>82</v>
@@ -32593,10 +32590,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -32622,10 +32619,10 @@
         <v>171</v>
       </c>
       <c r="L242" t="s" s="2">
+        <v>1052</v>
+      </c>
+      <c r="M242" t="s" s="2">
         <v>1053</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>1054</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -32655,11 +32652,11 @@
         <v>263</v>
       </c>
       <c r="Y242" t="s" s="2">
+        <v>1053</v>
+      </c>
+      <c r="Z242" t="s" s="2">
         <v>1054</v>
       </c>
-      <c r="Z242" t="s" s="2">
-        <v>1055</v>
-      </c>
       <c r="AA242" t="s" s="2">
         <v>82</v>
       </c>
@@ -32676,7 +32673,7 @@
         <v>82</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>91</v>
@@ -32694,7 +32691,7 @@
         <v>82</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="AM242" t="s" s="2">
         <v>109</v>
